--- a/MapFiles/KeyBinds.xlsx
+++ b/MapFiles/KeyBinds.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\Den\OneDrive\Personal\Thrustmaster\TARGET\Clicker\Development\ED_TargetScript-503\Maps\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\Den\OneDrive\Personal\Thrustmaster\TARGET\Clicker\Development\ED_Enhanced_Warthog\MapFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF099212-D4ED-4BF0-84E4-E71405A9D37B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2D3C42B-02BE-4C8E-B8B7-000EE5BA9DDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="690" yWindow="225" windowWidth="33450" windowHeight="18765" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4425" yWindow="645" windowWidth="31470" windowHeight="19215" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="In Ship" sheetId="1" r:id="rId1"/>
@@ -928,9 +928,6 @@
     <t>Clear Auth</t>
   </si>
   <si>
-    <t>Standard Unmodified Keys - v503</t>
-  </si>
-  <si>
     <t>Home</t>
   </si>
   <si>
@@ -944,6 +941,9 @@
   </si>
   <si>
     <t>???</t>
+  </si>
+  <si>
+    <t>Standard Unmodified Keys - v510</t>
   </si>
 </sst>
 </file>
@@ -1349,6 +1349,12 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1374,12 +1380,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1686,20 +1686,20 @@
   <sheetData>
     <row r="1" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="35" t="s">
-        <v>300</v>
-      </c>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
-      <c r="G2" s="36"/>
-      <c r="H2" s="36"/>
-      <c r="I2" s="36"/>
-      <c r="J2" s="36"/>
-      <c r="K2" s="36"/>
-      <c r="L2" s="36"/>
-      <c r="M2" s="37"/>
+      <c r="B2" s="37" t="s">
+        <v>305</v>
+      </c>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
+      <c r="I2" s="38"/>
+      <c r="J2" s="38"/>
+      <c r="K2" s="38"/>
+      <c r="L2" s="38"/>
+      <c r="M2" s="39"/>
     </row>
     <row r="3" spans="2:13" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
@@ -1736,7 +1736,7 @@
         <v>110</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.25">
@@ -2159,7 +2159,9 @@
       <c r="H15" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="I15" s="5"/>
+      <c r="I15" s="17" t="s">
+        <v>130</v>
+      </c>
       <c r="J15" s="4" t="s">
         <v>106</v>
       </c>
@@ -2211,9 +2213,7 @@
       <c r="B17" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="C17" s="17" t="s">
-        <v>130</v>
-      </c>
+      <c r="C17" s="5"/>
       <c r="D17" s="4">
         <v>4</v>
       </c>
@@ -2275,30 +2275,30 @@
     </row>
     <row r="19" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="20" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="38" t="s">
+      <c r="B20" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="C20" s="39"/>
-      <c r="D20" s="38" t="s">
+      <c r="C20" s="41"/>
+      <c r="D20" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="E20" s="39"/>
-      <c r="F20" s="38" t="s">
+      <c r="E20" s="41"/>
+      <c r="F20" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="G20" s="39"/>
-      <c r="H20" s="38" t="s">
+      <c r="G20" s="41"/>
+      <c r="H20" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="I20" s="39"/>
-      <c r="J20" s="38" t="s">
+      <c r="I20" s="41"/>
+      <c r="J20" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="K20" s="39"/>
-      <c r="L20" s="38" t="s">
+      <c r="K20" s="41"/>
+      <c r="L20" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="M20" s="39"/>
+      <c r="M20" s="41"/>
       <c r="N20"/>
       <c r="O20"/>
     </row>
@@ -2306,7 +2306,7 @@
       <c r="B21" s="2"/>
       <c r="C21" s="3"/>
       <c r="D21" s="2" t="s">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="E21" s="16" t="s">
         <v>44</v>
@@ -2643,10 +2643,10 @@
     <row r="37" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B37" s="4"/>
       <c r="C37" s="5"/>
-      <c r="D37" s="33" t="s">
+      <c r="D37" s="35" t="s">
         <v>204</v>
       </c>
-      <c r="E37" s="34"/>
+      <c r="E37" s="36"/>
       <c r="F37" s="2" t="s">
         <v>36</v>
       </c>
@@ -2860,11 +2860,11 @@
       <c r="C48" s="10"/>
       <c r="D48" s="9"/>
       <c r="E48" s="10"/>
-      <c r="F48" s="42" t="s">
-        <v>301</v>
+      <c r="F48" s="33" t="s">
+        <v>300</v>
       </c>
       <c r="G48" s="22" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H48" s="9"/>
       <c r="I48" s="10"/>
@@ -2878,11 +2878,11 @@
       <c r="C49" s="7"/>
       <c r="D49" s="6"/>
       <c r="E49" s="7"/>
-      <c r="F49" s="43" t="s">
-        <v>302</v>
+      <c r="F49" s="34" t="s">
+        <v>301</v>
       </c>
       <c r="G49" s="18" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H49" s="6"/>
       <c r="I49" s="7"/>
@@ -2931,20 +2931,20 @@
   <sheetData>
     <row r="1" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="35" t="s">
+      <c r="B2" s="37" t="s">
         <v>298</v>
       </c>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
-      <c r="G2" s="36"/>
-      <c r="H2" s="36"/>
-      <c r="I2" s="36"/>
-      <c r="J2" s="36"/>
-      <c r="K2" s="36"/>
-      <c r="L2" s="36"/>
-      <c r="M2" s="37"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
+      <c r="I2" s="38"/>
+      <c r="J2" s="38"/>
+      <c r="K2" s="38"/>
+      <c r="L2" s="38"/>
+      <c r="M2" s="39"/>
     </row>
     <row r="3" spans="2:13" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B3" s="26" t="s">
@@ -3462,10 +3462,10 @@
     </row>
     <row r="19" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="20" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="40" t="s">
+      <c r="B20" s="42" t="s">
         <v>278</v>
       </c>
-      <c r="C20" s="41"/>
+      <c r="C20" s="43"/>
     </row>
     <row r="21" spans="2:13" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B21" s="26" t="s">
